--- a/planning/드립백_원가표.xlsx
+++ b/planning/드립백_원가표.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0\개"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -125,6 +125,11 @@
     </font>
     <font>
       <name val="Pretendard"/>
+    </font>
+    <font>
+      <name val="Pretendard"/>
+      <color rgb="00A2401C"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -179,7 +184,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -343,6 +348,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="26" min="1" max="1"/>
@@ -649,11 +655,11 @@
     <row r="5" ht="15" customHeight="1" s="27">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>라 에스메랄다 게이샤</t>
+          <t>허벌 블렌드</t>
         </is>
       </c>
       <c r="B5" s="32" t="n">
-        <v>1253</v>
+        <v>1037</v>
       </c>
       <c r="C5" s="32" t="n">
         <v>209</v>
@@ -664,6 +670,11 @@
       <c r="E5" s="33">
         <f>SUM(B5:D5)</f>
         <v/>
+      </c>
+      <c r="F5" s="59" t="inlineStr">
+        <is>
+          <t>10/28 수정: 싱글 게이샤(1,253) → 허벌 블렌드. 추정: 생두 (52,000×0.67 + 28,000×0.33) ÷ 0.85 = 51,859원/kg × 20g (원두주문_덤_이익.xlsx와 같은 가정)</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="27">
@@ -1175,7 +1186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="26" min="1" max="1"/>
@@ -1241,7 +1252,7 @@
     <row r="7" ht="15" customHeight="1" s="27">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>라 에스메랄다 게이샤</t>
+          <t>허벌 블렌드</t>
         </is>
       </c>
       <c r="B7" s="51">
@@ -1349,6 +1360,26 @@
       <c r="B14" s="55">
         <f>B11</f>
         <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>허벌 생두 나누기(배합 67:33): 게이샤 = D7×0.67, 카투라 = D7×0.33</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>ROUND(D7*0.67,2)</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>ROUND(D7*0.33,2)</f>
+        <v/>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>← 게이샤 kg / 카투라 kg</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/planning/드립백_원가표.xlsx
+++ b/planning/드립백_원가표.xlsx
@@ -625,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="27">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -655,7 +656,7 @@
     <row r="5" ht="15" customHeight="1" s="27">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>허벌 블렌드</t>
+          <t>허벌 블랜드</t>
         </is>
       </c>
       <c r="B5" s="32" t="n">
@@ -673,7 +674,7 @@
       </c>
       <c r="F5" s="59" t="inlineStr">
         <is>
-          <t>10/28 수정: 싱글 게이샤(1,253) → 허벌 블렌드. 추정: 생두 (52,000×0.67 + 28,000×0.33) ÷ 0.85 = 51,859원/kg × 20g (원두주문_덤_이익.xlsx와 같은 가정)</t>
+          <t>10/28 수정: 싱글 게이샤(1,253) → 허벌 블랜드. 추정: 생두 (52,000×0.67 + 28,000×0.33) ÷ 0.85 = 51,859원/kg × 20g (원두주문_덤_이익.xlsx와 같은 가정)</t>
         </is>
       </c>
     </row>
@@ -760,6 +761,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="27">
       <c r="A11" s="34" t="inlineStr">
         <is>
@@ -916,6 +918,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="15" customHeight="1" s="27">
       <c r="A25" s="34" t="inlineStr">
         <is>
@@ -967,6 +970,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="27">
       <c r="A31" s="42" t="inlineStr">
         <is>
@@ -1018,6 +1022,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="43" t="inlineStr">
         <is>
@@ -1202,6 +1207,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="27">
       <c r="A3" s="31" t="inlineStr">
         <is>
@@ -1227,6 +1233,7 @@
         <v>20</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="27">
       <c r="A6" s="30" t="inlineStr">
         <is>
@@ -1252,7 +1259,7 @@
     <row r="7" ht="15" customHeight="1" s="27">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>허벌 블렌드</t>
+          <t>허벌 블랜드</t>
         </is>
       </c>
       <c r="B7" s="51">
@@ -1344,6 +1351,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="27">
       <c r="A13" s="29" t="inlineStr">
         <is>
@@ -1362,21 +1370,22 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>허벌 생두 나누기(배합 67:33): 게이샤 = D7×0.67, 카투라 = D7×0.33</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="B16" s="26">
         <f>ROUND(D7*0.67,2)</f>
         <v/>
       </c>
-      <c r="C16">
+      <c r="C16" s="26">
         <f>ROUND(D7*0.33,2)</f>
         <v/>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>← 게이샤 kg / 카투라 kg</t>
         </is>
@@ -1410,6 +1419,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="27">
       <c r="A3" s="31" t="inlineStr">
         <is>
@@ -1500,6 +1510,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="27">
       <c r="A10" s="31" t="inlineStr">
         <is>
@@ -1555,6 +1566,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="27">
       <c r="A16" s="29" t="inlineStr">
         <is>
